--- a/artfynd/A 3786-2022 artfynd.xlsx
+++ b/artfynd/A 3786-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121591025</v>
+        <v>121591026</v>
       </c>
       <c r="B2" t="n">
-        <v>91996</v>
+        <v>103619</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>222412</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>733819</v>
+        <v>734017</v>
       </c>
       <c r="R2" t="n">
-        <v>7358865</v>
+        <v>7358698</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121591028</v>
+        <v>121591025</v>
       </c>
       <c r="B3" t="n">
-        <v>57509</v>
+        <v>91996</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,30 +793,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>734140</v>
+        <v>733819</v>
       </c>
       <c r="R3" t="n">
-        <v>7358746</v>
+        <v>7358865</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -861,11 +861,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-08-21</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Varnande läte</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121591026</v>
+        <v>121591028</v>
       </c>
       <c r="B4" t="n">
-        <v>103619</v>
+        <v>57509</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222412</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -936,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>734017</v>
+        <v>734140</v>
       </c>
       <c r="R4" t="n">
-        <v>7358698</v>
+        <v>7358746</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -972,6 +967,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-08-21</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Varnande läte</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 3786-2022 artfynd.xlsx
+++ b/artfynd/A 3786-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121591026</v>
+        <v>121591025</v>
       </c>
       <c r="B2" t="n">
-        <v>103619</v>
+        <v>91996</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222412</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>734017</v>
+        <v>733819</v>
       </c>
       <c r="R2" t="n">
-        <v>7358698</v>
+        <v>7358865</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121591025</v>
+        <v>121591026</v>
       </c>
       <c r="B3" t="n">
-        <v>91996</v>
+        <v>103619</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,26 +797,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>222412</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>733819</v>
+        <v>734017</v>
       </c>
       <c r="R3" t="n">
-        <v>7358865</v>
+        <v>7358698</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>

--- a/artfynd/A 3786-2022 artfynd.xlsx
+++ b/artfynd/A 3786-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121591025</v>
       </c>
       <c r="B2" t="n">
-        <v>91996</v>
+        <v>92004</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>121591026</v>
       </c>
       <c r="B3" t="n">
-        <v>103619</v>
+        <v>103627</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>121591028</v>
       </c>
       <c r="B4" t="n">
-        <v>57509</v>
+        <v>57510</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 3786-2022 artfynd.xlsx
+++ b/artfynd/A 3786-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121591025</v>
+        <v>121591026</v>
       </c>
       <c r="B2" t="n">
-        <v>92004</v>
+        <v>103627</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>222412</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>733819</v>
+        <v>734017</v>
       </c>
       <c r="R2" t="n">
-        <v>7358865</v>
+        <v>7358698</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121591026</v>
+        <v>121591025</v>
       </c>
       <c r="B3" t="n">
-        <v>103627</v>
+        <v>92004</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,26 +797,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222412</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>734017</v>
+        <v>733819</v>
       </c>
       <c r="R3" t="n">
-        <v>7358698</v>
+        <v>7358865</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>

--- a/artfynd/A 3786-2022 artfynd.xlsx
+++ b/artfynd/A 3786-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121591026</v>
+        <v>121591028</v>
       </c>
       <c r="B2" t="n">
-        <v>103627</v>
+        <v>57510</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222412</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>734017</v>
+        <v>734140</v>
       </c>
       <c r="R2" t="n">
-        <v>7358698</v>
+        <v>7358746</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -755,6 +755,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-08-21</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Varnande läte</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121591025</v>
+        <v>121591026</v>
       </c>
       <c r="B3" t="n">
-        <v>92004</v>
+        <v>103627</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,26 +802,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>222412</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -825,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>733819</v>
+        <v>734017</v>
       </c>
       <c r="R3" t="n">
-        <v>7358865</v>
+        <v>7358698</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -887,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121591028</v>
+        <v>121591025</v>
       </c>
       <c r="B4" t="n">
-        <v>57510</v>
+        <v>92004</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,30 +904,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -931,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>734140</v>
+        <v>733819</v>
       </c>
       <c r="R4" t="n">
-        <v>7358746</v>
+        <v>7358865</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -967,11 +972,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-08-21</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Varnande läte</t>
         </is>
       </c>
       <c r="AD4" t="b">
